--- a/Hasan Panwar/Student Attendance/Class ECE 1-New Att- Aug-Dec-24.xlsx
+++ b/Hasan Panwar/Student Attendance/Class ECE 1-New Att- Aug-Dec-24.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faysal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Hasan Panwar\Student Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D325C1-64C8-4641-86FF-DB69830F49EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE93BAD-93F7-4C3D-9A91-4F30F25B2999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="626" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="626" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="August" sheetId="23" r:id="rId1"/>
@@ -19,10 +19,19 @@
     <sheet name="November" sheetId="27" r:id="rId4"/>
     <sheet name="December" sheetId="29" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -678,16 +687,6 @@
   </cellStyles>
   <dxfs count="67">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
@@ -1090,9 +1089,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1142,6 +1144,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1488,38 +1497,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF883EB-F85F-45D5-92C8-DD6F8DBB1B1F}">
   <dimension ref="A1:AP46"/>
-  <sheetFormatPr defaultColWidth="3.81640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.26953125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="22" width="4.54296875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="3.7265625" style="1" customWidth="1"/>
-    <col min="37" max="38" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="3.81640625" style="1"/>
+    <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="22" width="4.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="3.7109375" style="1" customWidth="1"/>
+    <col min="37" max="38" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="32"/>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -1559,7 +1568,7 @@
       <c r="AK1" s="32"/>
       <c r="AL1" s="32"/>
     </row>
-    <row r="2" spans="1:42" ht="17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>21</v>
       </c>
@@ -1601,7 +1610,7 @@
       <c r="AK2" s="33"/>
       <c r="AL2" s="33"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
@@ -1754,7 +1763,7 @@
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -1864,7 +1873,7 @@
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -1948,7 +1957,7 @@
       </c>
       <c r="AP5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -2030,7 +2039,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -2108,7 +2117,7 @@
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -2188,7 +2197,7 @@
       <c r="AO8" s="30"/>
       <c r="AP8" s="31"/>
     </row>
-    <row r="9" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -2274,7 +2283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -2363,7 +2372,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -2452,7 +2461,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -2541,7 +2550,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -2619,7 +2628,7 @@
       <c r="AO13" s="11"/>
       <c r="AP13" s="11"/>
     </row>
-    <row r="14" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -2697,7 +2706,7 @@
       <c r="AO14" s="12"/>
       <c r="AP14" s="12"/>
     </row>
-    <row r="15" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -2775,7 +2784,7 @@
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -2855,7 +2864,7 @@
       <c r="AO16" s="30"/>
       <c r="AP16" s="31"/>
     </row>
-    <row r="17" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -2941,7 +2950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -3030,7 +3039,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -3119,7 +3128,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -3208,7 +3217,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -3282,7 +3291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -3356,7 +3365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -3428,7 +3437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -3502,7 +3511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -3574,7 +3583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -3648,7 +3657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -3722,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -3796,7 +3805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -3870,7 +3879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -3944,7 +3953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>27</v>
       </c>
@@ -4018,7 +4027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -4092,7 +4101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>29</v>
       </c>
@@ -4166,7 +4175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -4240,7 +4249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>31</v>
       </c>
@@ -4312,7 +4321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>32</v>
       </c>
@@ -4384,7 +4393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>33</v>
       </c>
@@ -4458,7 +4467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>34</v>
       </c>
@@ -4532,7 +4541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>35</v>
       </c>
@@ -4606,7 +4615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -4680,7 +4689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>37</v>
       </c>
@@ -4754,7 +4763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>38</v>
       </c>
@@ -4828,7 +4837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>39</v>
       </c>
@@ -4902,7 +4911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>40</v>
       </c>
@@ -4974,7 +4983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>41</v>
       </c>
@@ -5048,7 +5057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="E46" s="7" t="s">
         <v>104</v>
       </c>
@@ -5071,17 +5080,17 @@
   <conditionalFormatting sqref="B5:B35">
     <cfRule type="duplicateValues" dxfId="66" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P36:P45 I36:I45 T36:W45 F27:W35 X27:X45 F26:AC26 Y27:AC44 Y45:AH45 AD41:AH44 AG34:AI35 AD34:AF40 AG36:AH40 F3:AJ5 AD26:AI33 F6:AI25 AJ6:AJ45">
+  <conditionalFormatting sqref="F3:AJ5 F6:AI25 AJ6:AJ45 F26:AC26 AD26:AI33 F27:W35 Y27:AC44 X27:X45 AG34:AI35 AD34:AF40 AG36:AH40 I36:I45 P36:P45 T36:W45 AD41:AH44 Y45:AH45">
     <cfRule type="expression" dxfId="65" priority="11">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P36:P45 I36:I45 T36:W45 F27:W35 X27:X45 F26:AC26 Y27:AC44 Y45:AH45 AD41:AH44 AG34:AI35 AD34:AF40 AG36:AH40 F4:AJ5 AD26:AI33 F6:AI25 AJ6:AJ45">
+  <conditionalFormatting sqref="F4:AJ5 F6:AI25 AJ6:AJ45 F26:AC26 AD26:AI33 F27:W35 Y27:AC44 X27:X45 AG34:AI35 AD34:AF40 AG36:AH40 I36:I45 P36:P45 T36:W45 AD41:AH44 Y45:AH45">
     <cfRule type="expression" dxfId="64" priority="10">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P36:P45 I36:I45 T36:W45 F27:W35 X27:X45 F26:AC26 Y27:AC44 Y45:AH45 AD41:AH44 AG34:AI35 AD34:AF40 AG36:AH40 F5:AJ5 AD26:AI33 F6:AI25 AJ6:AJ45">
+  <conditionalFormatting sqref="F5:AJ5 F6:AI25 AJ6:AJ45 F26:AC26 AD26:AI33 F27:W35 Y27:AC44 X27:X45 AG34:AI35 AD34:AF40 AG36:AH40 I36:I45 P36:P45 T36:W45 AD41:AH44 Y45:AH45">
     <cfRule type="cellIs" dxfId="63" priority="7" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -5092,49 +5101,47 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AG35:AH40">
+    <cfRule type="expression" dxfId="60" priority="20">
+      <formula>AF$3="Sun"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="22">
+      <formula>IF(AF$4=TODAY(),TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AL3 AK5:AL45">
-    <cfRule type="expression" dxfId="60" priority="12">
+    <cfRule type="expression" dxfId="58" priority="12">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM6">
-    <cfRule type="expression" dxfId="59" priority="5">
+    <cfRule type="expression" dxfId="57" priority="5">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AM12">
-    <cfRule type="expression" dxfId="58" priority="3">
+    <cfRule type="expression" dxfId="56" priority="3">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AM20">
-    <cfRule type="expression" dxfId="57" priority="2">
+    <cfRule type="expression" dxfId="55" priority="2">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM4:AN4">
-    <cfRule type="expression" dxfId="56" priority="6">
+    <cfRule type="expression" dxfId="54" priority="6">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN9:AP9">
-    <cfRule type="expression" dxfId="55" priority="4">
+    <cfRule type="expression" dxfId="53" priority="4">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN17:AP17">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>#REF!="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG35:AH40">
-    <cfRule type="expression" dxfId="53" priority="20">
-      <formula>AF$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG35:AH40">
-    <cfRule type="expression" dxfId="52" priority="22">
-      <formula>IF(AF$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5145,42 +5152,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB6DFB9-03D3-4CD5-AC41-C920A9DB2B12}">
   <dimension ref="A1:AO46"/>
-  <sheetFormatPr defaultColWidth="3.81640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="2.7265625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="3" style="1" customWidth="1"/>
-    <col min="14" max="19" width="4.54296875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="3.54296875" style="1" customWidth="1"/>
-    <col min="21" max="22" width="4.54296875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="3.7265625" style="1" customWidth="1"/>
-    <col min="36" max="37" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.08984375" style="1" customWidth="1"/>
-    <col min="40" max="40" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="3.81640625" style="1"/>
+    <col min="14" max="19" width="4.5703125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="3.5703125" style="1" customWidth="1"/>
+    <col min="21" max="22" width="4.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="3.7109375" style="1" customWidth="1"/>
+    <col min="36" max="37" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.140625" style="1" customWidth="1"/>
+    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
@@ -5221,7 +5228,7 @@
       <c r="AJ1" s="32"/>
       <c r="AK1" s="32"/>
     </row>
-    <row r="2" spans="1:41" ht="17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>21</v>
       </c>
@@ -5262,7 +5269,7 @@
       <c r="AJ2" s="33"/>
       <c r="AK2" s="33"/>
     </row>
-    <row r="3" spans="1:41" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
@@ -5411,7 +5418,7 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" spans="1:41" ht="35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" ht="36" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -5518,7 +5525,7 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -5629,7 +5636,7 @@
       </c>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -5738,7 +5745,7 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -5843,7 +5850,7 @@
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
     </row>
-    <row r="8" spans="1:41" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -5950,7 +5957,7 @@
       <c r="AN8" s="30"/>
       <c r="AO8" s="31"/>
     </row>
-    <row r="9" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -6063,7 +6070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -6179,7 +6186,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -6295,7 +6302,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -6411,7 +6418,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -6516,7 +6523,7 @@
       <c r="AN13" s="11"/>
       <c r="AO13" s="11"/>
     </row>
-    <row r="14" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -6621,7 +6628,7 @@
       <c r="AN14" s="12"/>
       <c r="AO14" s="12"/>
     </row>
-    <row r="15" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -6726,7 +6733,7 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
     </row>
-    <row r="16" spans="1:41" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -6833,7 +6840,7 @@
       <c r="AN16" s="30"/>
       <c r="AO16" s="31"/>
     </row>
-    <row r="17" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -6946,7 +6953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -7062,7 +7069,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -7178,7 +7185,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -7294,7 +7301,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -7395,7 +7402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -7496,7 +7503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -7595,7 +7602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -7696,7 +7703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -7795,7 +7802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -7894,7 +7901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -7995,7 +8002,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -8096,7 +8103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -8197,7 +8204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -8298,7 +8305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>27</v>
       </c>
@@ -8399,7 +8406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -8500,7 +8507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>29</v>
       </c>
@@ -8601,7 +8608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -8702,7 +8709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>31</v>
       </c>
@@ -8803,7 +8810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>32</v>
       </c>
@@ -8902,7 +8909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>33</v>
       </c>
@@ -9001,7 +9008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>34</v>
       </c>
@@ -9102,7 +9109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>35</v>
       </c>
@@ -9203,7 +9210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -9304,7 +9311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>37</v>
       </c>
@@ -9405,7 +9412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>38</v>
       </c>
@@ -9506,7 +9513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>39</v>
       </c>
@@ -9607,7 +9614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>40</v>
       </c>
@@ -9708,7 +9715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>41</v>
       </c>
@@ -9807,7 +9814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>42</v>
       </c>
@@ -9924,64 +9931,64 @@
     <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
+  <conditionalFormatting sqref="B5:B38">
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F3:AI46">
-    <cfRule type="expression" dxfId="51" priority="12">
+    <cfRule type="expression" dxfId="50" priority="12">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:AI46">
-    <cfRule type="expression" dxfId="50" priority="11">
+    <cfRule type="expression" dxfId="49" priority="11">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:AI46">
-    <cfRule type="cellIs" dxfId="49" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="8" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="9" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK46">
-    <cfRule type="expression" dxfId="46" priority="13">
+    <cfRule type="expression" dxfId="45" priority="13">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL5:AL6">
-    <cfRule type="expression" dxfId="45" priority="6">
+    <cfRule type="expression" dxfId="44" priority="6">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL12">
-    <cfRule type="expression" dxfId="44" priority="4">
+    <cfRule type="expression" dxfId="43" priority="4">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL17:AL20">
-    <cfRule type="expression" dxfId="43" priority="3">
+    <cfRule type="expression" dxfId="42" priority="3">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AM4">
-    <cfRule type="expression" dxfId="42" priority="7">
+    <cfRule type="expression" dxfId="41" priority="7">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9">
-    <cfRule type="expression" dxfId="41" priority="5">
+    <cfRule type="expression" dxfId="40" priority="5">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AO17">
-    <cfRule type="expression" dxfId="40" priority="2">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>#REF!="Sun"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B38">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9991,38 +9998,38 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A603D02-B252-4D0E-B3C2-7647397784BF}">
   <dimension ref="A1:AP51"/>
-  <sheetFormatPr defaultColWidth="3.81640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="22" width="4.54296875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="3.7265625" style="1" customWidth="1"/>
-    <col min="37" max="38" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="3.81640625" style="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="22" width="4.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="3.7109375" style="1" customWidth="1"/>
+    <col min="37" max="38" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
@@ -10064,7 +10071,7 @@
       <c r="AK1" s="32"/>
       <c r="AL1" s="32"/>
     </row>
-    <row r="2" spans="1:42" ht="17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>29</v>
       </c>
@@ -10106,7 +10113,7 @@
       <c r="AK2" s="33"/>
       <c r="AL2" s="33"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
@@ -10259,7 +10266,7 @@
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -10369,7 +10376,7 @@
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -10489,7 +10496,7 @@
       </c>
       <c r="AP5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -10607,7 +10614,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -10721,7 +10728,7 @@
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -10837,7 +10844,7 @@
       <c r="AO8" s="30"/>
       <c r="AP8" s="31"/>
     </row>
-    <row r="9" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -10959,7 +10966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -11084,7 +11091,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -11209,7 +11216,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="12" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -11334,7 +11341,7 @@
         <v>0.35192307692307695</v>
       </c>
     </row>
-    <row r="13" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -11448,7 +11455,7 @@
       <c r="AO13" s="11"/>
       <c r="AP13" s="11"/>
     </row>
-    <row r="14" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -11562,7 +11569,7 @@
       <c r="AO14" s="12"/>
       <c r="AP14" s="12"/>
     </row>
-    <row r="15" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -11676,7 +11683,7 @@
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -11792,7 +11799,7 @@
       <c r="AO16" s="30"/>
       <c r="AP16" s="31"/>
     </row>
-    <row r="17" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -11914,7 +11921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -12039,7 +12046,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -12164,7 +12171,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -12289,7 +12296,7 @@
         <v>0.64807692307692311</v>
       </c>
     </row>
-    <row r="21" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -12399,7 +12406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -12509,7 +12516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -12617,7 +12624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -12727,7 +12734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -12835,7 +12842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -12943,7 +12950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -13051,7 +13058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -13159,7 +13166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -13269,7 +13276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -13379,7 +13386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>27</v>
       </c>
@@ -13489,7 +13496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:42" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -13599,7 +13606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>29</v>
       </c>
@@ -13709,7 +13716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -13819,7 +13826,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>31</v>
       </c>
@@ -13929,7 +13936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>32</v>
       </c>
@@ -14039,7 +14046,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>33</v>
       </c>
@@ -14147,7 +14154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>34</v>
       </c>
@@ -14255,7 +14262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>35</v>
       </c>
@@ -14365,7 +14372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -14475,7 +14482,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>37</v>
       </c>
@@ -14585,7 +14592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>38</v>
       </c>
@@ -14695,7 +14702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>39</v>
       </c>
@@ -14805,7 +14812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>40</v>
       </c>
@@ -14915,7 +14922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>41</v>
       </c>
@@ -15025,7 +15032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>42</v>
       </c>
@@ -15133,7 +15140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43</v>
       </c>
@@ -15241,7 +15248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>44</v>
       </c>
@@ -15349,7 +15356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>45</v>
       </c>
@@ -15457,7 +15464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:38" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>46</v>
       </c>
@@ -15565,7 +15572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>47</v>
       </c>
@@ -15688,64 +15695,64 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:B51">
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F3:AJ51">
-    <cfRule type="expression" dxfId="38" priority="17">
+    <cfRule type="expression" dxfId="37" priority="17">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:AJ51">
-    <cfRule type="expression" dxfId="37" priority="16">
+    <cfRule type="expression" dxfId="36" priority="16">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:AJ51">
-    <cfRule type="cellIs" dxfId="36" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="8" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AL3 AK5:AL51">
-    <cfRule type="expression" dxfId="33" priority="18">
+    <cfRule type="expression" dxfId="32" priority="18">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM6">
-    <cfRule type="expression" dxfId="32" priority="6">
+    <cfRule type="expression" dxfId="31" priority="6">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AM12">
-    <cfRule type="expression" dxfId="31" priority="4">
+    <cfRule type="expression" dxfId="30" priority="4">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AM20">
-    <cfRule type="expression" dxfId="30" priority="3">
+    <cfRule type="expression" dxfId="29" priority="3">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM4:AN4">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="28" priority="7">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN9:AP9">
-    <cfRule type="expression" dxfId="28" priority="5">
+    <cfRule type="expression" dxfId="27" priority="5">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN17:AP17">
-    <cfRule type="expression" dxfId="27" priority="2">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>#REF!="Sun"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B51">
-    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -15755,39 +15762,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6FE6AA-FD2A-4C0D-A31A-A1E0228EE4AE}">
   <dimension ref="A1:AO49"/>
-  <sheetFormatPr defaultColWidth="3.81640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="22" width="4.54296875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="3.7265625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="3.81640625" style="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="22" width="4.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="3.7109375" style="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
@@ -15828,7 +15835,7 @@
       <c r="AJ1" s="32"/>
       <c r="AK1" s="32"/>
     </row>
-    <row r="2" spans="1:41" ht="17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>21</v>
       </c>
@@ -15869,7 +15876,7 @@
       <c r="AJ2" s="33"/>
       <c r="AK2" s="33"/>
     </row>
-    <row r="3" spans="1:41" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
@@ -16018,7 +16025,7 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" spans="1:41" ht="36.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -16125,7 +16132,7 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -16240,7 +16247,7 @@
       </c>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -16353,7 +16360,7 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -16462,7 +16469,7 @@
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
     </row>
-    <row r="8" spans="1:41" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -16573,7 +16580,7 @@
       <c r="AN8" s="30"/>
       <c r="AO8" s="31"/>
     </row>
-    <row r="9" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -16690,7 +16697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -16810,7 +16817,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -16930,7 +16937,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -17050,7 +17057,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -17159,7 +17166,7 @@
       <c r="AN13" s="11"/>
       <c r="AO13" s="11"/>
     </row>
-    <row r="14" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -17268,7 +17275,7 @@
       <c r="AN14" s="12"/>
       <c r="AO14" s="12"/>
     </row>
-    <row r="15" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -17377,7 +17384,7 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
     </row>
-    <row r="16" spans="1:41" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -17488,7 +17495,7 @@
       <c r="AN16" s="30"/>
       <c r="AO16" s="31"/>
     </row>
-    <row r="17" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -17605,7 +17612,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -17725,7 +17732,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -17845,7 +17852,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -17965,7 +17972,7 @@
         <v>0.57499999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -18070,7 +18077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -18175,7 +18182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -18278,7 +18285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -18383,7 +18390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -18486,7 +18493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -18591,7 +18598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -18696,7 +18703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -18801,7 +18808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -18906,7 +18913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -19011,7 +19018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>27</v>
       </c>
@@ -19116,7 +19123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -19221,7 +19228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>29</v>
       </c>
@@ -19326,7 +19333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -19431,7 +19438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>31</v>
       </c>
@@ -19534,7 +19541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>32</v>
       </c>
@@ -19637,7 +19644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>33</v>
       </c>
@@ -19742,7 +19749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>34</v>
       </c>
@@ -19847,7 +19854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>35</v>
       </c>
@@ -19952,7 +19959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -20057,7 +20064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>37</v>
       </c>
@@ -20162,7 +20169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>38</v>
       </c>
@@ -20267,7 +20274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>39</v>
       </c>
@@ -20372,7 +20379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>40</v>
       </c>
@@ -20475,7 +20482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>41</v>
       </c>
@@ -20580,7 +20587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>42</v>
       </c>
@@ -20681,7 +20688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43</v>
       </c>
@@ -20780,7 +20787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A48" s="24"/>
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
@@ -20877,7 +20884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:37" x14ac:dyDescent="0.25">
       <c r="E49" s="7"/>
       <c r="F49" s="23" t="s">
         <v>23</v>
@@ -20985,64 +20992,64 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:B35">
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F3:AI49">
-    <cfRule type="expression" dxfId="25" priority="12">
+    <cfRule type="expression" dxfId="24" priority="12">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:AI49">
-    <cfRule type="expression" dxfId="24" priority="11">
+    <cfRule type="expression" dxfId="23" priority="11">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:AI49">
-    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK49">
-    <cfRule type="expression" dxfId="20" priority="13">
+    <cfRule type="expression" dxfId="19" priority="13">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL5:AL6">
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="18" priority="6">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL12">
-    <cfRule type="expression" dxfId="18" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL17:AL20">
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="16" priority="3">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AM4">
-    <cfRule type="expression" dxfId="16" priority="7">
+    <cfRule type="expression" dxfId="15" priority="7">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9">
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AO17">
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>#REF!="Sun"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B35">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -21052,39 +21059,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EC3481-E319-4156-A890-1C3A741719AF}">
   <dimension ref="A1:AO49"/>
-  <sheetFormatPr defaultColWidth="3.81640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="22" width="4.54296875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="3.7265625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="3.81640625" style="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="22" width="4.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="3.7109375" style="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
@@ -21125,7 +21132,7 @@
       <c r="AJ1" s="32"/>
       <c r="AK1" s="32"/>
     </row>
-    <row r="2" spans="1:41" ht="17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>21</v>
       </c>
@@ -21166,7 +21173,7 @@
       <c r="AJ2" s="33"/>
       <c r="AK2" s="33"/>
     </row>
-    <row r="3" spans="1:41" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
@@ -21315,7 +21322,7 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" spans="1:41" ht="36.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -21422,7 +21429,7 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -21485,7 +21492,7 @@
       </c>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -21546,7 +21553,7 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -21603,7 +21610,7 @@
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
     </row>
-    <row r="8" spans="1:41" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -21662,7 +21669,7 @@
       <c r="AN8" s="30"/>
       <c r="AO8" s="31"/>
     </row>
-    <row r="9" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -21727,7 +21734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -21795,7 +21802,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -21863,7 +21870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -21931,7 +21938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -21988,7 +21995,7 @@
       <c r="AN13" s="11"/>
       <c r="AO13" s="11"/>
     </row>
-    <row r="14" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -22045,7 +22052,7 @@
       <c r="AN14" s="12"/>
       <c r="AO14" s="12"/>
     </row>
-    <row r="15" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -22102,7 +22109,7 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
     </row>
-    <row r="16" spans="1:41" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -22161,7 +22168,7 @@
       <c r="AN16" s="30"/>
       <c r="AO16" s="31"/>
     </row>
-    <row r="17" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -22226,7 +22233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -22294,7 +22301,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -22362,7 +22369,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -22430,7 +22437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -22483,7 +22490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -22536,7 +22543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -22587,7 +22594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -22640,7 +22647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -22691,7 +22698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -22744,7 +22751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -22797,7 +22804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -22850,7 +22857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -22903,7 +22910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -22956,7 +22963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>27</v>
       </c>
@@ -23009,7 +23016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:41" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>28</v>
       </c>
@@ -23062,7 +23069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>29</v>
       </c>
@@ -23115,7 +23122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>30</v>
       </c>
@@ -23168,7 +23175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>31</v>
       </c>
@@ -23219,7 +23226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>32</v>
       </c>
@@ -23270,7 +23277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>33</v>
       </c>
@@ -23323,7 +23330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>34</v>
       </c>
@@ -23376,7 +23383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>35</v>
       </c>
@@ -23429,7 +23436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>36</v>
       </c>
@@ -23482,7 +23489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>37</v>
       </c>
@@ -23535,7 +23542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>38</v>
       </c>
@@ -23588,7 +23595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>39</v>
       </c>
@@ -23641,7 +23648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>40</v>
       </c>
@@ -23692,7 +23699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>41</v>
       </c>
@@ -23745,7 +23752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>42</v>
       </c>
@@ -23794,7 +23801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43</v>
       </c>
@@ -23841,7 +23848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A48" s="24"/>
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
@@ -23886,7 +23893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:37" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:37" x14ac:dyDescent="0.25">
       <c r="E49" s="7"/>
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
@@ -23941,64 +23948,64 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
   </mergeCells>
-  <conditionalFormatting sqref="F48:M49 O48:AI49 F3:AI47">
-    <cfRule type="expression" dxfId="12" priority="12">
+  <conditionalFormatting sqref="B5:B35">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AI47 F48:M49 O48:AI49">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F48:M49 O48:AI49 F4:AI47">
-    <cfRule type="expression" dxfId="11" priority="11">
+  <conditionalFormatting sqref="F4:AI47 F48:M49 O48:AI49">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F48:M49 O48:AI49 F5:AI47">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+  <conditionalFormatting sqref="F5:AI47 F48:M49 O48:AI49">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK49">
-    <cfRule type="expression" dxfId="7" priority="13">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL5:AL6">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL12">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL17:AL20">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AM4">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AO17">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>#REF!="Sun"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B35">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
